--- a/labs/lab-04-visualise-pay-and-placement-distributions-with-python-in-excel/data/BrightPath_Contract_Placements.xlsx
+++ b/labs/lab-04-visualise-pay-and-placement-distributions-with-python-in-excel/data/BrightPath_Contract_Placements.xlsx
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -80,6 +80,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8896,12 +8899,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -8939,7 +8942,367 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2 · A</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Add a column Gross_Margin_Pct to tblPlacements = (Bill_Rate_Hourly - Pay_Rate_Hourly) / Bill_Rate_Hourly, formatted as a percentage with 1 decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>2 · B</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>In an empty cell on Python_Charts, add this formula, tell me the result, and show the Gross_Margin_Pct calculation for the first row:
+=AVERAGE(tblPlacements[Gross_Margin_Pct])</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>3 · C</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Using Python in Excel, create a box plot of Bill_Rate_Hourly by Job_Level from tblPlacements, ordered Junior, Mid, Senior, Lead. Put it in Python_Charts!B2. Title it "Contract bill rate by job level (S$/hour)" and label both axes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>3 · D</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Which table and columns does the code in Python_Charts!B2 use, and in what order are the levels?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>3 · E</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>In the cell beside the box plot, add this formula and tell me if it matches the Lead median in the chart:
+=MEDIAN(FILTER(tblPlacements[Bill_Rate_Hourly],tblPlacements[Job_Level]="Lead"))</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>4 · F</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Using Python, create a scatter plot of Years_Experience (x) against Pay_Rate_Hourly (y) from tblPlacements, coloured by Job_Level, with a linear trend line. Also return the Pearson correlation coefficient in the cell below the chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>4 · G</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>In an empty cell below the scatter plot, add this formula and tell me if it matches the r you returned:
+=CORREL(tblPlacements[Years_Experience],tblPlacements[Pay_Rate_Hourly])</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>5 · H</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Using Python, create a heatmap of the average Gross_Margin_Pct by Sector (rows) and Job_Level (columns, ordered Junior to Lead) with the values printed in each cell as percentages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>5 · I</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Does the heatmap code use the mean of Gross_Margin_Pct for each Sector and Job_Level cell? Show that line of code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>6 · J</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Using the IQR rule (above Q3 + 1.5 x IQR), list the Pay_Rate_Hourly outliers in tblPlacements with Placement_ID, Sector, Job_Level and Pay_Rate_Hourly. State Q1, Q3 and the upper fence. Show the code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>6 · K</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Add a row to Prompt_Log for the highest Pay_Rate_Hourly outlier with my decision:
+&lt;error / genuine specialist rate / check with the desk&gt; and a one-line reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>7 · L</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Explain the Python code in Python_Charts!B2 line by line in plain English.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>7 · M</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Prompt_Log already lists every prompt in this lab. For each one I ran, fill in What Copilot did and How I verified, and set Decision to Keep. I will tell you any row to change to Revise or Undo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Extra 1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Add Gross_Margin_Pct = (Bill_Rate_Hourly - Pay_Rate_Hourly) / Bill_Rate_Hourly as a percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Extra 2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Using Python, create a box plot of Bill_Rate_Hourly by Job_Level ordered Junior, Mid, Senior, Lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Extra 3</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Using Python, create a histogram of Pay_Rate_Hourly with 15 bins and mark the median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Extra 4</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Using Python, plot Years_Experience against Pay_Rate_Hourly with a linear trend line and return the correlation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Extra 5</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Using Python, create a heatmap of average Gross_Margin_Pct by Sector and Job_Level with values shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Extra 6</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Using the IQR rule, list Pay_Rate_Hourly outliers with Placement_ID, Sector and Job_Level, and state the upper fence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Extra 7</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Explain the Python code in the selected cell line by line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Extra 8</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>What are the median and mean Bill_Rate_Hourly by Job_Level? Show the code.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
